--- a/templates/PRAP_SourceData_Template_v1.16.xlsx
+++ b/templates/PRAP_SourceData_Template_v1.16.xlsx
@@ -1465,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1521,8 +1521,7 @@
       <c r="D2" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>example row - delete before use</t>
         </is>
